--- a/condicionales.xlsx
+++ b/condicionales.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rstaffolani\Desktop\SALUD\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813D446D-36D0-49C8-8523-18AB42D4CB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BE699D-DC22-406B-9867-96A8A6A7E09C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{E2784FDD-D670-4CC9-8FD3-538CDC5E4A22}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="23">
   <si>
     <t>Regla</t>
   </si>
@@ -87,10 +87,13 @@
     <t>aplicar_canalizador_provincia</t>
   </si>
   <si>
+    <t>aplicar_rutas_red_diameld</t>
+  </si>
+  <si>
     <t>no</t>
   </si>
   <si>
-    <t>aplicar_rutas_red_diameld</t>
+    <t>aplicar_geo_direcciones_puntuales</t>
   </si>
 </sst>
 </file>
@@ -456,10 +459,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{746E806A-40AE-4DE5-99F6-87F739080711}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.7265625" customWidth="1"/>
+    <col min="1" max="1" width="31.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
@@ -483,7 +486,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -600,9 +603,17 @@
     </row>
     <row r="18" spans="1:2" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>17</v>
       </c>
     </row>
